--- a/预测水位/OutputData/SK05.xlsx
+++ b/预测水位/OutputData/SK05.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -695,9 +695,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1046,11 +1043,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2161"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B2221"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="22.8916666666667" customWidth="1"/>
+    <col min="2" max="2" width="25.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -18252,99 +18249,541 @@
       </c>
     </row>
     <row r="2150" spans="1:2">
-      <c r="A2150" s="7">
+      <c r="A2150" s="5">
         <v>45837</v>
       </c>
-      <c r="B2150" s="8">
+      <c r="B2150" s="6">
         <v>591.719</v>
       </c>
     </row>
     <row r="2151" spans="1:2">
-      <c r="A2151" s="7">
+      <c r="A2151" s="5">
         <v>45837.0833333333</v>
       </c>
-      <c r="B2151" s="8">
+      <c r="B2151" s="6">
         <v>591.728</v>
       </c>
     </row>
     <row r="2152" spans="1:2">
-      <c r="A2152" s="7">
+      <c r="A2152" s="5">
         <v>45837.1666666667</v>
       </c>
-      <c r="B2152" s="8">
+      <c r="B2152" s="6">
         <v>591.73</v>
       </c>
     </row>
     <row r="2153" spans="1:2">
-      <c r="A2153" s="7">
+      <c r="A2153" s="5">
         <v>45837.25</v>
       </c>
-      <c r="B2153" s="8">
+      <c r="B2153" s="6">
         <v>591.721</v>
       </c>
     </row>
     <row r="2154" spans="1:2">
-      <c r="A2154" s="7">
+      <c r="A2154" s="5">
         <v>45837.3333333333</v>
       </c>
-      <c r="B2154" s="8">
+      <c r="B2154" s="6">
         <v>591.7</v>
       </c>
     </row>
     <row r="2155" spans="1:2">
-      <c r="A2155" s="7">
+      <c r="A2155" s="5">
         <v>45837.4166666667</v>
       </c>
-      <c r="B2155" s="8">
+      <c r="B2155" s="6">
         <v>591.676</v>
       </c>
     </row>
     <row r="2156" spans="1:2">
-      <c r="A2156" s="7">
+      <c r="A2156" s="5">
         <v>45837.5</v>
       </c>
-      <c r="B2156" s="8">
+      <c r="B2156" s="6">
         <v>591.661</v>
       </c>
     </row>
     <row r="2157" spans="1:2">
-      <c r="A2157" s="7">
+      <c r="A2157" s="5">
         <v>45837.5833333333</v>
       </c>
-      <c r="B2157" s="8">
+      <c r="B2157" s="6">
         <v>591.65</v>
       </c>
     </row>
     <row r="2158" spans="1:2">
-      <c r="A2158" s="7">
+      <c r="A2158" s="5">
         <v>45837.6666666667</v>
       </c>
-      <c r="B2158" s="8">
+      <c r="B2158" s="6">
         <v>591.642</v>
       </c>
     </row>
     <row r="2159" spans="1:2">
-      <c r="A2159" s="7">
+      <c r="A2159" s="5">
         <v>45837.75</v>
       </c>
-      <c r="B2159" s="8">
+      <c r="B2159" s="6">
         <v>591.643</v>
       </c>
     </row>
     <row r="2160" spans="1:2">
-      <c r="A2160" s="7">
+      <c r="A2160" s="5">
         <v>45837.8333333333</v>
       </c>
-      <c r="B2160" s="8">
+      <c r="B2160" s="6">
         <v>591.641</v>
       </c>
     </row>
     <row r="2161" spans="1:2">
-      <c r="A2161" s="7">
+      <c r="A2161" s="5">
         <v>45837.9166666667</v>
       </c>
-      <c r="B2161" s="8">
+      <c r="B2161" s="6">
         <v>591.647</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:2">
+      <c r="A2162" s="5">
+        <v>45838</v>
+      </c>
+      <c r="B2162" s="6">
+        <v>591.657</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:2">
+      <c r="A2163" s="5">
+        <v>45838.0833333333</v>
+      </c>
+      <c r="B2163" s="6"/>
+    </row>
+    <row r="2164" spans="1:2">
+      <c r="A2164" s="5">
+        <v>45838.1666666667</v>
+      </c>
+      <c r="B2164" s="6">
+        <v>591.661</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:2">
+      <c r="A2165" s="5">
+        <v>45838.25</v>
+      </c>
+      <c r="B2165" s="6">
+        <v>591.644</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:2">
+      <c r="A2166" s="5">
+        <v>45838.3333333333</v>
+      </c>
+      <c r="B2166" s="6">
+        <v>591.625</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:2">
+      <c r="A2167" s="5">
+        <v>45838.4166666667</v>
+      </c>
+      <c r="B2167" s="6">
+        <v>591.614</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:2">
+      <c r="A2168" s="5">
+        <v>45838.5</v>
+      </c>
+      <c r="B2168" s="6">
+        <v>591.601</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:2">
+      <c r="A2169" s="5">
+        <v>45838.5833333333</v>
+      </c>
+      <c r="B2169" s="6">
+        <v>591.591</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:2">
+      <c r="A2170" s="5">
+        <v>45838.6666666667</v>
+      </c>
+      <c r="B2170" s="6">
+        <v>591.581</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:2">
+      <c r="A2171" s="5">
+        <v>45838.75</v>
+      </c>
+      <c r="B2171" s="6">
+        <v>591.579</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:2">
+      <c r="A2172" s="5">
+        <v>45838.8333333333</v>
+      </c>
+      <c r="B2172" s="6">
+        <v>591.583</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:2">
+      <c r="A2173" s="5">
+        <v>45838.9166666667</v>
+      </c>
+      <c r="B2173" s="6">
+        <v>591.584</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:2">
+      <c r="A2174" s="5">
+        <v>45839</v>
+      </c>
+      <c r="B2174" s="6">
+        <v>591.589</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:2">
+      <c r="A2175" s="5">
+        <v>45839.0833333333</v>
+      </c>
+      <c r="B2175" s="6">
+        <v>591.584</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:2">
+      <c r="A2176" s="5">
+        <v>45839.1666666667</v>
+      </c>
+      <c r="B2176" s="6">
+        <v>591.566</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:2">
+      <c r="A2177" s="5">
+        <v>45839.25</v>
+      </c>
+      <c r="B2177" s="6">
+        <v>591.524</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:2">
+      <c r="A2178" s="5">
+        <v>45839.3333333333</v>
+      </c>
+      <c r="B2178" s="6">
+        <v>591.519</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:2">
+      <c r="A2179" s="5">
+        <v>45839.4166666667</v>
+      </c>
+      <c r="B2179" s="6">
+        <v>591.51</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:2">
+      <c r="A2180" s="5">
+        <v>45839.5</v>
+      </c>
+      <c r="B2180" s="6">
+        <v>591.484</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:2">
+      <c r="A2181" s="5">
+        <v>45839.5833333333</v>
+      </c>
+      <c r="B2181" s="6">
+        <v>591.446</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:2">
+      <c r="A2182" s="5">
+        <v>45839.6666666667</v>
+      </c>
+      <c r="B2182" s="6">
+        <v>591.483</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:2">
+      <c r="A2183" s="5">
+        <v>45839.75</v>
+      </c>
+      <c r="B2183" s="6">
+        <v>591.486</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:2">
+      <c r="A2184" s="5">
+        <v>45839.8333333333</v>
+      </c>
+      <c r="B2184" s="6">
+        <v>591.491</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:2">
+      <c r="A2185" s="5">
+        <v>45839.9166666667</v>
+      </c>
+      <c r="B2185" s="6">
+        <v>591.497</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:2">
+      <c r="A2186" s="5">
+        <v>45840</v>
+      </c>
+      <c r="B2186" s="6">
+        <v>591.505</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:2">
+      <c r="A2187" s="5">
+        <v>45840.0833333333</v>
+      </c>
+      <c r="B2187" s="6">
+        <v>591.498</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:2">
+      <c r="A2188" s="5">
+        <v>45840.1666666667</v>
+      </c>
+      <c r="B2188" s="6">
+        <v>591.471</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:2">
+      <c r="A2189" s="5">
+        <v>45840.25</v>
+      </c>
+      <c r="B2189" s="6">
+        <v>591.456</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:2">
+      <c r="A2190" s="5">
+        <v>45840.3333333333</v>
+      </c>
+      <c r="B2190" s="6">
+        <v>591.442</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:2">
+      <c r="A2191" s="5">
+        <v>45840.4166666667</v>
+      </c>
+      <c r="B2191" s="6">
+        <v>591.439</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:2">
+      <c r="A2192" s="5">
+        <v>45840.5</v>
+      </c>
+      <c r="B2192" s="6">
+        <v>591.428</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:2">
+      <c r="A2193" s="5">
+        <v>45840.5833333333</v>
+      </c>
+      <c r="B2193" s="6">
+        <v>591.413</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:2">
+      <c r="A2194" s="5">
+        <v>45840.6666666667</v>
+      </c>
+      <c r="B2194" s="6">
+        <v>591.395</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:2">
+      <c r="A2195" s="5">
+        <v>45840.75</v>
+      </c>
+      <c r="B2195" s="6">
+        <v>591.399</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:2">
+      <c r="A2196" s="5">
+        <v>45840.8333333333</v>
+      </c>
+      <c r="B2196" s="6">
+        <v>591.416</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:2">
+      <c r="A2197" s="5">
+        <v>45840.9166666667</v>
+      </c>
+      <c r="B2197" s="6">
+        <v>591.432</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:2">
+      <c r="A2198" s="5">
+        <v>45841</v>
+      </c>
+      <c r="B2198" s="6">
+        <v>591.44</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:2">
+      <c r="A2199" s="5">
+        <v>45841.0833333333</v>
+      </c>
+      <c r="B2199" s="6">
+        <v>591.441</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:2">
+      <c r="A2200" s="5">
+        <v>45841.1666666667</v>
+      </c>
+      <c r="B2200" s="6">
+        <v>591.416</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:2">
+      <c r="A2201" s="5">
+        <v>45841.25</v>
+      </c>
+      <c r="B2201" s="6">
+        <v>591.39</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:2">
+      <c r="A2202" s="5">
+        <v>45841.3333333333</v>
+      </c>
+      <c r="B2202" s="6">
+        <v>591.367</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:2">
+      <c r="A2203" s="5">
+        <v>45841.4166666667</v>
+      </c>
+      <c r="B2203" s="6">
+        <v>591.361</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:2">
+      <c r="A2204" s="5">
+        <v>45841.5</v>
+      </c>
+      <c r="B2204" s="6">
+        <v>591.338</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:2">
+      <c r="A2205" s="5">
+        <v>45841.5833333333</v>
+      </c>
+      <c r="B2205" s="6">
+        <v>591.322</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:2">
+      <c r="A2206" s="5">
+        <v>45841.6666666667</v>
+      </c>
+      <c r="B2206" s="6">
+        <v>591.291</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:2">
+      <c r="A2207" s="5">
+        <v>45841.75</v>
+      </c>
+      <c r="B2207" s="6">
+        <v>591.279</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:2">
+      <c r="A2208" s="5">
+        <v>45841.8333333333</v>
+      </c>
+      <c r="B2208" s="6">
+        <v>591.284</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:2">
+      <c r="A2209" s="5">
+        <v>45841.9166666667</v>
+      </c>
+      <c r="B2209" s="6">
+        <v>591.285</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:1">
+      <c r="A2210" s="7">
+        <v>45842</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:1">
+      <c r="A2211" s="7">
+        <v>45842.0833333333</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:1">
+      <c r="A2212" s="7">
+        <v>45842.1666666667</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:1">
+      <c r="A2213" s="7">
+        <v>45842.25</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:1">
+      <c r="A2214" s="7">
+        <v>45842.3333333333</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:1">
+      <c r="A2215" s="7">
+        <v>45842.4166666667</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:1">
+      <c r="A2216" s="7">
+        <v>45842.5</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:1">
+      <c r="A2217" s="7">
+        <v>45842.5833333333</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:1">
+      <c r="A2218" s="7">
+        <v>45842.6666666667</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:1">
+      <c r="A2219" s="7">
+        <v>45842.75</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:1">
+      <c r="A2220" s="7">
+        <v>45842.8333333333</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:1">
+      <c r="A2221" s="7">
+        <v>45842.9166666667</v>
       </c>
     </row>
   </sheetData>
